--- a/public/student_bulk_upload_sample.xlsx
+++ b/public/student_bulk_upload_sample.xlsx
@@ -1,41 +1,818 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eb10c0d4cb0a459f/Desktop/Language-Lab-Backend/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_E82743358F983D5D8C6002FA60D6B0DFA12C58FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Students" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="262">
+  <si>
+    <t>full_name</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>roll_no</t>
+  </si>
+  <si>
+    <t>enrollment_no</t>
+  </si>
+  <si>
+    <t>segment</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>Aarav Sharma</t>
+  </si>
+  <si>
+    <t>aarav.sharma@college.com</t>
+  </si>
+  <si>
+    <t>9800000001</t>
+  </si>
+  <si>
+    <t>DIP1001</t>
+  </si>
+  <si>
+    <t>EN2024001</t>
+  </si>
+  <si>
+    <t>Diploma</t>
+  </si>
+  <si>
+    <t>Aditi Desai</t>
+  </si>
+  <si>
+    <t>aditi.desai@college.com</t>
+  </si>
+  <si>
+    <t>9800000002</t>
+  </si>
+  <si>
+    <t>DEG2002</t>
+  </si>
+  <si>
+    <t>EN2024002</t>
+  </si>
+  <si>
+    <t>Degree</t>
+  </si>
+  <si>
+    <t>Akash Patil</t>
+  </si>
+  <si>
+    <t>akash.patil@college.com</t>
+  </si>
+  <si>
+    <t>9800000003</t>
+  </si>
+  <si>
+    <t>ENG3003</t>
+  </si>
+  <si>
+    <t>EN2024003</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Ananya Verma</t>
+  </si>
+  <si>
+    <t>ananya.verma@college.com</t>
+  </si>
+  <si>
+    <t>9800000004</t>
+  </si>
+  <si>
+    <t>ART4004</t>
+  </si>
+  <si>
+    <t>EN2024004</t>
+  </si>
+  <si>
+    <t>Arts</t>
+  </si>
+  <si>
+    <t>Anil Mehta</t>
+  </si>
+  <si>
+    <t>anil.mehta@college.com</t>
+  </si>
+  <si>
+    <t>9800000005</t>
+  </si>
+  <si>
+    <t>COM1005</t>
+  </si>
+  <si>
+    <t>EN2024005</t>
+  </si>
+  <si>
+    <t>Commerce</t>
+  </si>
+  <si>
+    <t>Anjali Joshi</t>
+  </si>
+  <si>
+    <t>anjali.joshi@college.com</t>
+  </si>
+  <si>
+    <t>9800000006</t>
+  </si>
+  <si>
+    <t>DIP2006</t>
+  </si>
+  <si>
+    <t>EN2024006</t>
+  </si>
+  <si>
+    <t>Arjun Rao</t>
+  </si>
+  <si>
+    <t>arjun.rao@college.com</t>
+  </si>
+  <si>
+    <t>9800000007</t>
+  </si>
+  <si>
+    <t>DEG3007</t>
+  </si>
+  <si>
+    <t>EN2024007</t>
+  </si>
+  <si>
+    <t>Ashwini Singh</t>
+  </si>
+  <si>
+    <t>ashwini.singh@college.com</t>
+  </si>
+  <si>
+    <t>9800000008</t>
+  </si>
+  <si>
+    <t>ENG4008</t>
+  </si>
+  <si>
+    <t>EN2024008</t>
+  </si>
+  <si>
+    <t>Bhavna Kumar</t>
+  </si>
+  <si>
+    <t>bhavna.kumar@college.com</t>
+  </si>
+  <si>
+    <t>9800000009</t>
+  </si>
+  <si>
+    <t>ART1009</t>
+  </si>
+  <si>
+    <t>EN2024009</t>
+  </si>
+  <si>
+    <t>Chirag Gupta</t>
+  </si>
+  <si>
+    <t>chirag.gupta@college.com</t>
+  </si>
+  <si>
+    <t>9800000010</t>
+  </si>
+  <si>
+    <t>COM2010</t>
+  </si>
+  <si>
+    <t>EN2024010</t>
+  </si>
+  <si>
+    <t>Deepa Shah</t>
+  </si>
+  <si>
+    <t>deepa.shah@college.com</t>
+  </si>
+  <si>
+    <t>9800000011</t>
+  </si>
+  <si>
+    <t>DIP3011</t>
+  </si>
+  <si>
+    <t>EN2024011</t>
+  </si>
+  <si>
+    <t>Divya Nair</t>
+  </si>
+  <si>
+    <t>divya.nair@college.com</t>
+  </si>
+  <si>
+    <t>9800000012</t>
+  </si>
+  <si>
+    <t>DEG4012</t>
+  </si>
+  <si>
+    <t>EN2024012</t>
+  </si>
+  <si>
+    <t>Ganesh Reddy</t>
+  </si>
+  <si>
+    <t>ganesh.reddy@college.com</t>
+  </si>
+  <si>
+    <t>9800000013</t>
+  </si>
+  <si>
+    <t>ENG1013</t>
+  </si>
+  <si>
+    <t>EN2024013</t>
+  </si>
+  <si>
+    <t>Heena Iyer</t>
+  </si>
+  <si>
+    <t>heena.iyer@college.com</t>
+  </si>
+  <si>
+    <t>9800000014</t>
+  </si>
+  <si>
+    <t>ART2014</t>
+  </si>
+  <si>
+    <t>EN2024014</t>
+  </si>
+  <si>
+    <t>Ishaan Patel</t>
+  </si>
+  <si>
+    <t>ishaan.patel@college.com</t>
+  </si>
+  <si>
+    <t>9800000015</t>
+  </si>
+  <si>
+    <t>COM3015</t>
+  </si>
+  <si>
+    <t>EN2024015</t>
+  </si>
+  <si>
+    <t>Jaya More</t>
+  </si>
+  <si>
+    <t>jaya.more@college.com</t>
+  </si>
+  <si>
+    <t>9800000016</t>
+  </si>
+  <si>
+    <t>DIP4016</t>
+  </si>
+  <si>
+    <t>EN2024016</t>
+  </si>
+  <si>
+    <t>Kiran Shinde</t>
+  </si>
+  <si>
+    <t>kiran.shinde@college.com</t>
+  </si>
+  <si>
+    <t>9800000017</t>
+  </si>
+  <si>
+    <t>DEG1017</t>
+  </si>
+  <si>
+    <t>EN2024017</t>
+  </si>
+  <si>
+    <t>Komal Jadhav</t>
+  </si>
+  <si>
+    <t>komal.jadhav@college.com</t>
+  </si>
+  <si>
+    <t>9800000018</t>
+  </si>
+  <si>
+    <t>ENG2018</t>
+  </si>
+  <si>
+    <t>EN2024018</t>
+  </si>
+  <si>
+    <t>Lakshmi Naik</t>
+  </si>
+  <si>
+    <t>lakshmi.naik@college.com</t>
+  </si>
+  <si>
+    <t>9800000019</t>
+  </si>
+  <si>
+    <t>ART3019</t>
+  </si>
+  <si>
+    <t>EN2024019</t>
+  </si>
+  <si>
+    <t>Manish Sawant</t>
+  </si>
+  <si>
+    <t>manish.sawant@college.com</t>
+  </si>
+  <si>
+    <t>9800000020</t>
+  </si>
+  <si>
+    <t>COM4020</t>
+  </si>
+  <si>
+    <t>EN2024020</t>
+  </si>
+  <si>
+    <t>Meera Kulkarni</t>
+  </si>
+  <si>
+    <t>meera.kulkarni@college.com</t>
+  </si>
+  <si>
+    <t>9800000021</t>
+  </si>
+  <si>
+    <t>DIP1021</t>
+  </si>
+  <si>
+    <t>EN2024021</t>
+  </si>
+  <si>
+    <t>Mohit Pawar</t>
+  </si>
+  <si>
+    <t>mohit.pawar@college.com</t>
+  </si>
+  <si>
+    <t>9800000022</t>
+  </si>
+  <si>
+    <t>DEG2022</t>
+  </si>
+  <si>
+    <t>EN2024022</t>
+  </si>
+  <si>
+    <t>Naina Gaikwad</t>
+  </si>
+  <si>
+    <t>naina.gaikwad@college.com</t>
+  </si>
+  <si>
+    <t>9800000023</t>
+  </si>
+  <si>
+    <t>ENG3023</t>
+  </si>
+  <si>
+    <t>EN2024023</t>
+  </si>
+  <si>
+    <t>Neha Mane</t>
+  </si>
+  <si>
+    <t>neha.mane@college.com</t>
+  </si>
+  <si>
+    <t>9800000024</t>
+  </si>
+  <si>
+    <t>ART4024</t>
+  </si>
+  <si>
+    <t>EN2024024</t>
+  </si>
+  <si>
+    <t>Nikhil Bhosale</t>
+  </si>
+  <si>
+    <t>nikhil.bhosale@college.com</t>
+  </si>
+  <si>
+    <t>9800000025</t>
+  </si>
+  <si>
+    <t>COM1025</t>
+  </si>
+  <si>
+    <t>EN2024025</t>
+  </si>
+  <si>
+    <t>Omkar Kadam</t>
+  </si>
+  <si>
+    <t>omkar.kadam@college.com</t>
+  </si>
+  <si>
+    <t>9800000026</t>
+  </si>
+  <si>
+    <t>DIP2026</t>
+  </si>
+  <si>
+    <t>EN2024026</t>
+  </si>
+  <si>
+    <t>Pooja Wagh</t>
+  </si>
+  <si>
+    <t>pooja.wagh@college.com</t>
+  </si>
+  <si>
+    <t>9800000027</t>
+  </si>
+  <si>
+    <t>DEG3027</t>
+  </si>
+  <si>
+    <t>EN2024027</t>
+  </si>
+  <si>
+    <t>Prachi Salve</t>
+  </si>
+  <si>
+    <t>prachi.salve@college.com</t>
+  </si>
+  <si>
+    <t>9800000028</t>
+  </si>
+  <si>
+    <t>ENG4028</t>
+  </si>
+  <si>
+    <t>EN2024028</t>
+  </si>
+  <si>
+    <t>Pratik Bankar</t>
+  </si>
+  <si>
+    <t>pratik.bankar@college.com</t>
+  </si>
+  <si>
+    <t>9800000029</t>
+  </si>
+  <si>
+    <t>ART1029</t>
+  </si>
+  <si>
+    <t>EN2024029</t>
+  </si>
+  <si>
+    <t>Priya Thorat</t>
+  </si>
+  <si>
+    <t>priya.thorat@college.com</t>
+  </si>
+  <si>
+    <t>9800000030</t>
+  </si>
+  <si>
+    <t>COM2030</t>
+  </si>
+  <si>
+    <t>EN2024030</t>
+  </si>
+  <si>
+    <t>Rahul Jagtap</t>
+  </si>
+  <si>
+    <t>rahul.jagtap@college.com</t>
+  </si>
+  <si>
+    <t>9800000031</t>
+  </si>
+  <si>
+    <t>DIP3031</t>
+  </si>
+  <si>
+    <t>EN2024031</t>
+  </si>
+  <si>
+    <t>Rajesh Sutar</t>
+  </si>
+  <si>
+    <t>rajesh.sutar@college.com</t>
+  </si>
+  <si>
+    <t>9800000032</t>
+  </si>
+  <si>
+    <t>DEG4032</t>
+  </si>
+  <si>
+    <t>EN2024032</t>
+  </si>
+  <si>
+    <t>Ravi Deshpande</t>
+  </si>
+  <si>
+    <t>ravi.deshpande@college.com</t>
+  </si>
+  <si>
+    <t>9800000033</t>
+  </si>
+  <si>
+    <t>ENG1033</t>
+  </si>
+  <si>
+    <t>EN2024033</t>
+  </si>
+  <si>
+    <t>Rohan Lokhande</t>
+  </si>
+  <si>
+    <t>rohan.lokhande@college.com</t>
+  </si>
+  <si>
+    <t>9800000034</t>
+  </si>
+  <si>
+    <t>ART2034</t>
+  </si>
+  <si>
+    <t>EN2024034</t>
+  </si>
+  <si>
+    <t>Rohini Gavhane</t>
+  </si>
+  <si>
+    <t>rohini.gavhane@college.com</t>
+  </si>
+  <si>
+    <t>9800000035</t>
+  </si>
+  <si>
+    <t>COM3035</t>
+  </si>
+  <si>
+    <t>EN2024035</t>
+  </si>
+  <si>
+    <t>Sachin Nikam</t>
+  </si>
+  <si>
+    <t>sachin.nikam@college.com</t>
+  </si>
+  <si>
+    <t>9800000036</t>
+  </si>
+  <si>
+    <t>DIP4036</t>
+  </si>
+  <si>
+    <t>EN2024036</t>
+  </si>
+  <si>
+    <t>Sagar Gite</t>
+  </si>
+  <si>
+    <t>sagar.gite@college.com</t>
+  </si>
+  <si>
+    <t>9800000037</t>
+  </si>
+  <si>
+    <t>DEG1037</t>
+  </si>
+  <si>
+    <t>EN2024037</t>
+  </si>
+  <si>
+    <t>Sangeeta Kale</t>
+  </si>
+  <si>
+    <t>sangeeta.kale@college.com</t>
+  </si>
+  <si>
+    <t>9800000038</t>
+  </si>
+  <si>
+    <t>ENG2038</t>
+  </si>
+  <si>
+    <t>EN2024038</t>
+  </si>
+  <si>
+    <t>Sanjay Bagal</t>
+  </si>
+  <si>
+    <t>sanjay.bagal@college.com</t>
+  </si>
+  <si>
+    <t>9800000039</t>
+  </si>
+  <si>
+    <t>ART3039</t>
+  </si>
+  <si>
+    <t>EN2024039</t>
+  </si>
+  <si>
+    <t>Sneha Chavan</t>
+  </si>
+  <si>
+    <t>sneha.chavan@college.com</t>
+  </si>
+  <si>
+    <t>9800000040</t>
+  </si>
+  <si>
+    <t>COM4040</t>
+  </si>
+  <si>
+    <t>EN2024040</t>
+  </si>
+  <si>
+    <t>Sonal Dhavale</t>
+  </si>
+  <si>
+    <t>sonal.dhavale@college.com</t>
+  </si>
+  <si>
+    <t>9800000041</t>
+  </si>
+  <si>
+    <t>DIP1041</t>
+  </si>
+  <si>
+    <t>EN2024041</t>
+  </si>
+  <si>
+    <t>Suresh Borde</t>
+  </si>
+  <si>
+    <t>suresh.borde@college.com</t>
+  </si>
+  <si>
+    <t>9800000042</t>
+  </si>
+  <si>
+    <t>DEG2042</t>
+  </si>
+  <si>
+    <t>EN2024042</t>
+  </si>
+  <si>
+    <t>Swati Ghuge</t>
+  </si>
+  <si>
+    <t>swati.ghuge@college.com</t>
+  </si>
+  <si>
+    <t>9800000043</t>
+  </si>
+  <si>
+    <t>ENG3043</t>
+  </si>
+  <si>
+    <t>EN2024043</t>
+  </si>
+  <si>
+    <t>Tanvi Kshirsagar</t>
+  </si>
+  <si>
+    <t>tanvi.kshirsagar@college.com</t>
+  </si>
+  <si>
+    <t>9800000044</t>
+  </si>
+  <si>
+    <t>ART4044</t>
+  </si>
+  <si>
+    <t>EN2024044</t>
+  </si>
+  <si>
+    <t>Tejas Misal</t>
+  </si>
+  <si>
+    <t>tejas.misal@college.com</t>
+  </si>
+  <si>
+    <t>9800000045</t>
+  </si>
+  <si>
+    <t>COM1045</t>
+  </si>
+  <si>
+    <t>EN2024045</t>
+  </si>
+  <si>
+    <t>Usha Parab</t>
+  </si>
+  <si>
+    <t>usha.parab@college.com</t>
+  </si>
+  <si>
+    <t>9800000046</t>
+  </si>
+  <si>
+    <t>DIP2046</t>
+  </si>
+  <si>
+    <t>EN2024046</t>
+  </si>
+  <si>
+    <t>Varsha Tambe</t>
+  </si>
+  <si>
+    <t>varsha.tambe@college.com</t>
+  </si>
+  <si>
+    <t>9800000047</t>
+  </si>
+  <si>
+    <t>DEG3047</t>
+  </si>
+  <si>
+    <t>EN2024047</t>
+  </si>
+  <si>
+    <t>Vikas Walke</t>
+  </si>
+  <si>
+    <t>vikas.walke@college.com</t>
+  </si>
+  <si>
+    <t>9800000048</t>
+  </si>
+  <si>
+    <t>ENG4048</t>
+  </si>
+  <si>
+    <t>EN2024048</t>
+  </si>
+  <si>
+    <t>Vishal Zende</t>
+  </si>
+  <si>
+    <t>vishal.zende@college.com</t>
+  </si>
+  <si>
+    <t>9800000049</t>
+  </si>
+  <si>
+    <t>ART1049</t>
+  </si>
+  <si>
+    <t>EN2024049</t>
+  </si>
+  <si>
+    <t>Yogesh Yadav</t>
+  </si>
+  <si>
+    <t>yogesh.yadav@college.com</t>
+  </si>
+  <si>
+    <t>9800000050</t>
+  </si>
+  <si>
+    <t>COM2050</t>
+  </si>
+  <si>
+    <t>EN2024050</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +842,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,58 +1181,1195 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G51"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="32.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="6.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>full_name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>email</v>
-      </c>
-      <c r="C1" t="str">
-        <v>phone</v>
-      </c>
-      <c r="D1" t="str">
-        <v>roll_no</v>
-      </c>
-      <c r="E1" t="str">
-        <v>enrollment_no</v>
-      </c>
-      <c r="F1" t="str">
-        <v>segment</v>
-      </c>
-      <c r="G1" t="str">
-        <v>year</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>John Doe</v>
-      </c>
-      <c r="B2" t="str">
-        <v>john@example.com</v>
-      </c>
-      <c r="C2" t="str">
-        <v>9876543210</v>
-      </c>
-      <c r="D2" t="str">
-        <v>ST001</v>
-      </c>
-      <c r="E2" t="str">
-        <v>EN001</v>
-      </c>
-      <c r="F2" t="str">
-        <v>A1</v>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>2026</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" t="s">
+        <v>91</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" t="s">
+        <v>96</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" t="s">
+        <v>101</v>
+      </c>
+      <c r="F19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" t="s">
+        <v>105</v>
+      </c>
+      <c r="E20" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" t="s">
+        <v>110</v>
+      </c>
+      <c r="E21" t="s">
+        <v>111</v>
+      </c>
+      <c r="F21" t="s">
+        <v>36</v>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" t="s">
+        <v>115</v>
+      </c>
+      <c r="E22" t="s">
+        <v>116</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" t="s">
+        <v>119</v>
+      </c>
+      <c r="D23" t="s">
+        <v>120</v>
+      </c>
+      <c r="E23" t="s">
+        <v>121</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" t="s">
+        <v>124</v>
+      </c>
+      <c r="D24" t="s">
+        <v>125</v>
+      </c>
+      <c r="E24" t="s">
+        <v>126</v>
+      </c>
+      <c r="F24" t="s">
+        <v>24</v>
+      </c>
+      <c r="G24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" t="s">
+        <v>128</v>
+      </c>
+      <c r="C25" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" t="s">
+        <v>130</v>
+      </c>
+      <c r="E25" t="s">
+        <v>131</v>
+      </c>
+      <c r="F25" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26" t="s">
+        <v>133</v>
+      </c>
+      <c r="C26" t="s">
+        <v>134</v>
+      </c>
+      <c r="D26" t="s">
+        <v>135</v>
+      </c>
+      <c r="E26" t="s">
+        <v>136</v>
+      </c>
+      <c r="F26" t="s">
+        <v>36</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>137</v>
+      </c>
+      <c r="B27" t="s">
+        <v>138</v>
+      </c>
+      <c r="C27" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27" t="s">
+        <v>140</v>
+      </c>
+      <c r="E27" t="s">
+        <v>141</v>
+      </c>
+      <c r="F27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>142</v>
+      </c>
+      <c r="B28" t="s">
+        <v>143</v>
+      </c>
+      <c r="C28" t="s">
+        <v>144</v>
+      </c>
+      <c r="D28" t="s">
+        <v>145</v>
+      </c>
+      <c r="E28" t="s">
+        <v>146</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>147</v>
+      </c>
+      <c r="B29" t="s">
+        <v>148</v>
+      </c>
+      <c r="C29" t="s">
+        <v>149</v>
+      </c>
+      <c r="D29" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" t="s">
+        <v>151</v>
+      </c>
+      <c r="F29" t="s">
+        <v>24</v>
+      </c>
+      <c r="G29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>152</v>
+      </c>
+      <c r="B30" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" t="s">
+        <v>154</v>
+      </c>
+      <c r="D30" t="s">
+        <v>155</v>
+      </c>
+      <c r="E30" t="s">
+        <v>156</v>
+      </c>
+      <c r="F30" t="s">
+        <v>30</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>157</v>
+      </c>
+      <c r="B31" t="s">
+        <v>158</v>
+      </c>
+      <c r="C31" t="s">
+        <v>159</v>
+      </c>
+      <c r="D31" t="s">
+        <v>160</v>
+      </c>
+      <c r="E31" t="s">
+        <v>161</v>
+      </c>
+      <c r="F31" t="s">
+        <v>36</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" t="s">
+        <v>163</v>
+      </c>
+      <c r="C32" t="s">
+        <v>164</v>
+      </c>
+      <c r="D32" t="s">
+        <v>165</v>
+      </c>
+      <c r="E32" t="s">
+        <v>166</v>
+      </c>
+      <c r="F32" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>167</v>
+      </c>
+      <c r="B33" t="s">
+        <v>168</v>
+      </c>
+      <c r="C33" t="s">
+        <v>169</v>
+      </c>
+      <c r="D33" t="s">
+        <v>170</v>
+      </c>
+      <c r="E33" t="s">
+        <v>171</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>172</v>
+      </c>
+      <c r="B34" t="s">
+        <v>173</v>
+      </c>
+      <c r="C34" t="s">
+        <v>174</v>
+      </c>
+      <c r="D34" t="s">
+        <v>175</v>
+      </c>
+      <c r="E34" t="s">
+        <v>176</v>
+      </c>
+      <c r="F34" t="s">
+        <v>24</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>177</v>
+      </c>
+      <c r="B35" t="s">
+        <v>178</v>
+      </c>
+      <c r="C35" t="s">
+        <v>179</v>
+      </c>
+      <c r="D35" t="s">
+        <v>180</v>
+      </c>
+      <c r="E35" t="s">
+        <v>181</v>
+      </c>
+      <c r="F35" t="s">
+        <v>30</v>
+      </c>
+      <c r="G35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>182</v>
+      </c>
+      <c r="B36" t="s">
+        <v>183</v>
+      </c>
+      <c r="C36" t="s">
+        <v>184</v>
+      </c>
+      <c r="D36" t="s">
+        <v>185</v>
+      </c>
+      <c r="E36" t="s">
+        <v>186</v>
+      </c>
+      <c r="F36" t="s">
+        <v>36</v>
+      </c>
+      <c r="G36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>187</v>
+      </c>
+      <c r="B37" t="s">
+        <v>188</v>
+      </c>
+      <c r="C37" t="s">
+        <v>189</v>
+      </c>
+      <c r="D37" t="s">
+        <v>190</v>
+      </c>
+      <c r="E37" t="s">
+        <v>191</v>
+      </c>
+      <c r="F37" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>192</v>
+      </c>
+      <c r="B38" t="s">
+        <v>193</v>
+      </c>
+      <c r="C38" t="s">
+        <v>194</v>
+      </c>
+      <c r="D38" t="s">
+        <v>195</v>
+      </c>
+      <c r="E38" t="s">
+        <v>196</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>197</v>
+      </c>
+      <c r="B39" t="s">
+        <v>198</v>
+      </c>
+      <c r="C39" t="s">
+        <v>199</v>
+      </c>
+      <c r="D39" t="s">
+        <v>200</v>
+      </c>
+      <c r="E39" t="s">
+        <v>201</v>
+      </c>
+      <c r="F39" t="s">
+        <v>24</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>202</v>
+      </c>
+      <c r="B40" t="s">
+        <v>203</v>
+      </c>
+      <c r="C40" t="s">
+        <v>204</v>
+      </c>
+      <c r="D40" t="s">
+        <v>205</v>
+      </c>
+      <c r="E40" t="s">
+        <v>206</v>
+      </c>
+      <c r="F40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>207</v>
+      </c>
+      <c r="B41" t="s">
+        <v>208</v>
+      </c>
+      <c r="C41" t="s">
+        <v>209</v>
+      </c>
+      <c r="D41" t="s">
+        <v>210</v>
+      </c>
+      <c r="E41" t="s">
+        <v>211</v>
+      </c>
+      <c r="F41" t="s">
+        <v>36</v>
+      </c>
+      <c r="G41">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>212</v>
+      </c>
+      <c r="B42" t="s">
+        <v>213</v>
+      </c>
+      <c r="C42" t="s">
+        <v>214</v>
+      </c>
+      <c r="D42" t="s">
+        <v>215</v>
+      </c>
+      <c r="E42" t="s">
+        <v>216</v>
+      </c>
+      <c r="F42" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>217</v>
+      </c>
+      <c r="B43" t="s">
+        <v>218</v>
+      </c>
+      <c r="C43" t="s">
+        <v>219</v>
+      </c>
+      <c r="D43" t="s">
+        <v>220</v>
+      </c>
+      <c r="E43" t="s">
+        <v>221</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>222</v>
+      </c>
+      <c r="B44" t="s">
+        <v>223</v>
+      </c>
+      <c r="C44" t="s">
+        <v>224</v>
+      </c>
+      <c r="D44" t="s">
+        <v>225</v>
+      </c>
+      <c r="E44" t="s">
+        <v>226</v>
+      </c>
+      <c r="F44" t="s">
+        <v>24</v>
+      </c>
+      <c r="G44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>227</v>
+      </c>
+      <c r="B45" t="s">
+        <v>228</v>
+      </c>
+      <c r="C45" t="s">
+        <v>229</v>
+      </c>
+      <c r="D45" t="s">
+        <v>230</v>
+      </c>
+      <c r="E45" t="s">
+        <v>231</v>
+      </c>
+      <c r="F45" t="s">
+        <v>30</v>
+      </c>
+      <c r="G45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>232</v>
+      </c>
+      <c r="B46" t="s">
+        <v>233</v>
+      </c>
+      <c r="C46" t="s">
+        <v>234</v>
+      </c>
+      <c r="D46" t="s">
+        <v>235</v>
+      </c>
+      <c r="E46" t="s">
+        <v>236</v>
+      </c>
+      <c r="F46" t="s">
+        <v>36</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>237</v>
+      </c>
+      <c r="B47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C47" t="s">
+        <v>239</v>
+      </c>
+      <c r="D47" t="s">
+        <v>240</v>
+      </c>
+      <c r="E47" t="s">
+        <v>241</v>
+      </c>
+      <c r="F47" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>242</v>
+      </c>
+      <c r="B48" t="s">
+        <v>243</v>
+      </c>
+      <c r="C48" t="s">
+        <v>244</v>
+      </c>
+      <c r="D48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E48" t="s">
+        <v>246</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>247</v>
+      </c>
+      <c r="B49" t="s">
+        <v>248</v>
+      </c>
+      <c r="C49" t="s">
+        <v>249</v>
+      </c>
+      <c r="D49" t="s">
+        <v>250</v>
+      </c>
+      <c r="E49" t="s">
+        <v>251</v>
+      </c>
+      <c r="F49" t="s">
+        <v>24</v>
+      </c>
+      <c r="G49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>252</v>
+      </c>
+      <c r="B50" t="s">
+        <v>253</v>
+      </c>
+      <c r="C50" t="s">
+        <v>254</v>
+      </c>
+      <c r="D50" t="s">
+        <v>255</v>
+      </c>
+      <c r="E50" t="s">
+        <v>256</v>
+      </c>
+      <c r="F50" t="s">
+        <v>30</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>257</v>
+      </c>
+      <c r="B51" t="s">
+        <v>258</v>
+      </c>
+      <c r="C51" t="s">
+        <v>259</v>
+      </c>
+      <c r="D51" t="s">
+        <v>260</v>
+      </c>
+      <c r="E51" t="s">
+        <v>261</v>
+      </c>
+      <c r="F51" t="s">
+        <v>36</v>
+      </c>
+      <c r="G51">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError sqref="A1:G51" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>